--- a/Planering 2026 LGIF.xlsx
+++ b/Planering 2026 LGIF.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b03121f1c8fff4a1/Barnen/Fotboll/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766B31D3-C8B9-44D8-9FE2-CA48FF061816}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13935" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matcher" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matcher!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Matcher!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="135">
   <si>
     <t>Datum</t>
   </si>
@@ -415,9 +415,6 @@
     <t>Bergumsvallen Konstgräs</t>
   </si>
   <si>
-    <t>00:00:00</t>
-  </si>
-  <si>
     <t>Slättadamm 2 konstgräs</t>
   </si>
   <si>
@@ -446,6 +443,27 @@
   </si>
   <si>
     <t>HC flyttad Båt 17:05_ 20:30</t>
+  </si>
+  <si>
+    <t>Måndag</t>
+  </si>
+  <si>
+    <t>F16</t>
+  </si>
+  <si>
+    <t>Örebrocup dag 1</t>
+  </si>
+  <si>
+    <t>Örebrocup dag 3</t>
+  </si>
+  <si>
+    <t>Örebrocup dag 2</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Majvallen 1</t>
   </si>
 </sst>
 </file>
@@ -561,7 +579,71 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4C7C3"/>
+          <bgColor rgb="FFF4C7C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE8B2"/>
+          <bgColor rgb="FFFCE8B2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -840,7 +922,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q1001"/>
+  <dimension ref="A1:Q1004"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1458,13 +1540,13 @@
     </row>
     <row r="16" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
-        <v>46136</v>
+        <v>46153</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>55</v>
+      <c r="C16" s="6">
+        <v>0.82291666666666663</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -1495,12 +1577,8 @@
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
@@ -1672,8 +1750,8 @@
       <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>47</v>
+      <c r="C21" s="6">
+        <v>0.82291666666666663</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>60</v>
@@ -1694,7 +1772,7 @@
         <v>88</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
@@ -1837,7 +1915,7 @@
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>7</v>
@@ -2164,309 +2242,274 @@
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
-        <v>46168</v>
+        <v>46186</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="6">
-        <v>0.76041666666666663</v>
-      </c>
+      <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="3">
-        <v>60713039</v>
-      </c>
-      <c r="G33" s="3">
-        <v>10</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>103</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K33" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>53</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="3" t="s">
-        <v>128</v>
-      </c>
+      <c r="P33" s="3"/>
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
-        <v>46189</v>
+        <v>46187</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="3">
-        <v>60220067</v>
-      </c>
-      <c r="G34" s="3">
-        <v>12</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K34" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4" t="s">
-        <v>107</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="3">
+        <v>60713039</v>
+      </c>
+      <c r="G36" s="3">
+        <v>10</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="3">
+        <v>60220067</v>
+      </c>
+      <c r="G37" s="3">
+        <v>12</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="2">
         <v>46196</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F38" s="3">
         <v>60220077</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G38" s="3">
         <v>13</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-    </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-    </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="P37" s="4" t="s">
+      <c r="K38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="7"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+    </row>
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="P40" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="7"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8"/>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-    </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="2">
-        <v>46245</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="3">
-        <v>60220080</v>
-      </c>
-      <c r="G39" s="3">
-        <v>14</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-    </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="2">
-        <v>46253</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F40" s="3">
-        <v>60716043</v>
-      </c>
-      <c r="G40" s="3">
-        <v>11</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-    </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="2">
-        <v>46257</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="3">
-        <v>60220087</v>
-      </c>
-      <c r="G41" s="3">
-        <v>15</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="K41" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46259</v>
+        <v>46245</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>7</v>
@@ -2481,16 +2524,16 @@
         <v>44</v>
       </c>
       <c r="F42" s="3">
-        <v>60220093</v>
+        <v>60220080</v>
       </c>
       <c r="G42" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>57</v>
@@ -2505,138 +2548,132 @@
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F43" s="3">
-        <v>60713048</v>
+        <v>60716043</v>
       </c>
       <c r="G43" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F44" s="3">
-        <v>60716048</v>
+        <v>60220087</v>
       </c>
       <c r="G44" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="K44" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L44" s="4"/>
-      <c r="M44" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
-        <v>46266</v>
+        <v>46259</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F45" s="3">
-        <v>60716052</v>
+        <v>60220093</v>
       </c>
       <c r="G45" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="K45" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>48</v>
@@ -2645,80 +2682,80 @@
         <v>49</v>
       </c>
       <c r="F46" s="3">
-        <v>60713051</v>
+        <v>60713048</v>
       </c>
       <c r="G46" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="L46" s="4"/>
       <c r="M46" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
-        <v>46271</v>
+        <v>46261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F47" s="3">
-        <v>60220097</v>
+        <v>60716048</v>
       </c>
       <c r="G47" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="K47" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
+      <c r="M47" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
     </row>
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
-        <v>46275</v>
+        <v>46266</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>60</v>
@@ -2727,43 +2764,41 @@
         <v>61</v>
       </c>
       <c r="F48" s="3">
-        <v>60716055</v>
+        <v>60716052</v>
       </c>
       <c r="G48" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="K48" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>52</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="N48" s="3"/>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="O48" s="3"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46275</v>
+        <v>46267</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
@@ -2772,19 +2807,19 @@
         <v>49</v>
       </c>
       <c r="F49" s="3">
-        <v>60713054</v>
+        <v>60713051</v>
       </c>
       <c r="G49" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="K49" s="3" t="b">
         <v>1</v>
@@ -2793,86 +2828,80 @@
         <v>52</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N49" s="3"/>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="O49" s="3"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>46283</v>
+        <v>46271</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F50" s="3">
-        <v>60716058</v>
+        <v>60220097</v>
       </c>
       <c r="G50" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K50" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F51" s="3">
-        <v>60713060</v>
+        <v>60716055</v>
       </c>
       <c r="G51" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="K51" s="3" t="b">
         <v>1</v>
@@ -2881,43 +2910,43 @@
         <v>52</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F52" s="3">
-        <v>60220113</v>
+        <v>60713054</v>
       </c>
       <c r="G52" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
@@ -2925,60 +2954,66 @@
       <c r="L52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M52" s="3"/>
+      <c r="M52" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>55</v>
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.84375</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F53" s="3">
-        <v>60220119</v>
+        <v>60716058</v>
       </c>
       <c r="G53" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="K53" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -2987,125 +3022,125 @@
         <v>49</v>
       </c>
       <c r="F54" s="3">
-        <v>60713064</v>
+        <v>60713060</v>
       </c>
       <c r="G54" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="4"/>
+      <c r="L54" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="M54" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46290</v>
+        <v>46281</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F55" s="3">
-        <v>60716062</v>
+        <v>60220113</v>
       </c>
       <c r="G55" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
+      <c r="L55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46297</v>
+        <v>46287</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F56" s="3">
-        <v>60716068</v>
+        <v>60220119</v>
       </c>
       <c r="G56" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46297</v>
+        <v>46289</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
@@ -3114,82 +3149,80 @@
         <v>49</v>
       </c>
       <c r="F57" s="3">
-        <v>60713066</v>
+        <v>60713064</v>
       </c>
       <c r="G57" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="L57" s="4"/>
       <c r="M57" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46299</v>
+        <v>46290</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F58" s="3">
-        <v>60220122</v>
+        <v>60716062</v>
       </c>
       <c r="G58" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
+      <c r="M58" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>60</v>
@@ -3198,39 +3231,43 @@
         <v>61</v>
       </c>
       <c r="F59" s="3">
-        <v>60716069</v>
+        <v>60716068</v>
       </c>
       <c r="G59" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L59" s="4"/>
+      <c r="L59" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="M59" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -3239,39 +3276,43 @@
         <v>49</v>
       </c>
       <c r="F60" s="3">
-        <v>60713071</v>
+        <v>60713066</v>
       </c>
       <c r="G60" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L60" s="4"/>
+      <c r="L60" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="M60" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>43</v>
@@ -3280,19 +3321,19 @@
         <v>44</v>
       </c>
       <c r="F61" s="3">
-        <v>60220132</v>
+        <v>60220122</v>
       </c>
       <c r="G61" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
@@ -3302,9 +3343,127 @@
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
     </row>
-    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F62" s="3">
+        <v>60716069</v>
+      </c>
+      <c r="G62" s="3">
+        <v>18</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" s="4"/>
+      <c r="M62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+    </row>
+    <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F63" s="3">
+        <v>60713071</v>
+      </c>
+      <c r="G63" s="3">
+        <v>18</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" s="4"/>
+      <c r="M63" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+    </row>
+    <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="3">
+        <v>60220132</v>
+      </c>
+      <c r="G64" s="3">
+        <v>22</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+    </row>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4242,36 +4401,65 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:O61" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <conditionalFormatting sqref="A2:O61 P8:P9 P11:P12 P15:P16 P32">
-    <cfRule type="expression" dxfId="7" priority="1">
+  <autoFilter ref="A1:O64" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <conditionalFormatting sqref="A2:O33 P8:P9 P11:P12 P15:P16 P32:P35 A34:D35 F34:O35 A36:O64">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$O2="ALLA TRE (DAM+VIT+SVART)"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$O2="DAM-VIT"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="13" priority="3">
       <formula>$O2="DAM-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>$O2="VIT-SVART"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>AND($O2&lt;&gt;"",ISNUMBER(SEARCH(",",$O2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>$D2="Dam"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>$D2="Vit"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$D2="Svart"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E34:E35">
+    <cfRule type="expression" dxfId="7" priority="25">
+      <formula>$O33="ALLA TRE (DAM+VIT+SVART)"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="26">
+      <formula>$O33="DAM-VIT"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="27">
+      <formula>$O33="DAM-SVART"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="28">
+      <formula>$O33="VIT-SVART"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="29">
+      <formula>AND($O33&lt;&gt;"",ISNUMBER(SEARCH(",",$O33)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="30">
+      <formula>$D33="Dam"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="31">
+      <formula>$D33="Vit"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="32">
+      <formula>$D33="Svart"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.16824335806944998" right="0.33648671613889997" top="9.6139061753971425E-2" bottom="0.20429550622718926" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Planering 2026 LGIF.xlsx
+++ b/Planering 2026 LGIF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b03121f1c8fff4a1/Barnen/Fotboll/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766B31D3-C8B9-44D8-9FE2-CA48FF061816}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{162264C3-A86B-4EBF-9E05-4244304888EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6984F25-7942-4ED3-A3CD-B2A8F02F8168}"/>
   <bookViews>
-    <workbookView xWindow="-13935" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matcher" sheetId="2" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="134">
   <si>
     <t>Datum</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t>Södra Skärgårdens IK F11-12</t>
-  </si>
-  <si>
-    <t>12:15:00</t>
   </si>
   <si>
     <t>Öjersjö IF</t>
@@ -563,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -573,8 +570,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1316,34 +1318,34 @@
     </row>
     <row r="11" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
-        <v>46130</v>
+        <v>46126</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3">
-        <v>60716005</v>
+        <v>60220016</v>
       </c>
       <c r="G11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="K11" s="3" t="b">
         <v>1</v>
@@ -1351,11 +1353,9 @@
       <c r="L11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3" t="s">
@@ -1364,68 +1364,66 @@
     </row>
     <row r="12" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F12" s="3">
-        <v>60220016</v>
+        <v>60713007</v>
       </c>
       <c r="G12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O12" s="3"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
       <c r="P12" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3">
-        <v>60713007</v>
+        <v>60716005</v>
       </c>
       <c r="G13" s="3">
         <v>2</v>
@@ -1434,7 +1432,7 @@
         <v>36</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>57</v>
@@ -1442,12 +1440,16 @@
       <c r="K13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
+      <c r="L13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
@@ -1540,13 +1542,13 @@
     </row>
     <row r="16" spans="1:17" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
-        <v>46153</v>
+        <v>46140</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.82291666666666663</v>
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>43</v>
@@ -1555,88 +1557,88 @@
         <v>44</v>
       </c>
       <c r="F16" s="3">
-        <v>60220020</v>
+        <v>60220026</v>
       </c>
       <c r="G16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="K16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" s="3">
-        <v>60220026</v>
+        <v>60713016</v>
       </c>
       <c r="G17" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="K17" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="M17" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
-        <v>46141</v>
+        <v>46144</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.60416666666666663</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F18" s="3">
-        <v>60713016</v>
+        <v>60716014</v>
       </c>
       <c r="G18" s="3">
         <v>4</v>
@@ -1645,7 +1647,7 @@
         <v>36</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>57</v>
@@ -1655,38 +1657,38 @@
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="3" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
     <row r="19" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.60416666666666663</v>
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3">
-        <v>60716014</v>
+        <v>60220033</v>
       </c>
       <c r="G19" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>57</v>
@@ -1695,9 +1697,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="4"/>
-      <c r="M19" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="3" t="s">
@@ -1706,111 +1706,113 @@
     </row>
     <row r="20" spans="1:16" ht="14.25" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.82291666666666663</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F20" s="3">
-        <v>60220033</v>
+        <v>60716017</v>
       </c>
       <c r="G20" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="K20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
+      <c r="M20" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
     <row r="21" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.82291666666666663</v>
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F21" s="3">
-        <v>60716017</v>
+        <v>60713019</v>
       </c>
       <c r="G21" s="3">
         <v>5</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="K21" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>55</v>
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.82291666666666663</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3">
-        <v>60713019</v>
+        <v>60220020</v>
       </c>
       <c r="G22" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>57</v>
@@ -1818,22 +1820,22 @@
       <c r="K22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
+      <c r="L22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>47</v>
+      <c r="C23" s="6">
+        <v>0.84375</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>48</v>
@@ -1864,7 +1866,9 @@
         <v>77</v>
       </c>
       <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
+      <c r="O23" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="P23" s="4" t="s">
         <v>92</v>
       </c>
@@ -2036,111 +2040,115 @@
     </row>
     <row r="28" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="3">
+        <v>60713039</v>
+      </c>
+      <c r="G28" s="3">
         <v>10</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="3">
-        <v>60220052</v>
-      </c>
-      <c r="G28" s="3">
-        <v>9</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="K28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="L28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" s="3"/>
     </row>
     <row r="29" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F29" s="3">
-        <v>60716032</v>
+        <v>60220052</v>
       </c>
       <c r="G29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="K29" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L29" s="4"/>
-      <c r="M29" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F30" s="3">
-        <v>60220060</v>
+        <v>60716032</v>
       </c>
       <c r="G30" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>57</v>
@@ -2149,37 +2157,39 @@
         <v>1</v>
       </c>
       <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
+      <c r="M30" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
-        <v>46180</v>
+        <v>46175</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F31" s="3">
-        <v>60713035</v>
+        <v>60220060</v>
       </c>
       <c r="G31" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>57</v>
@@ -2188,56 +2198,52 @@
         <v>1</v>
       </c>
       <c r="L31" s="4"/>
-      <c r="M31" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
-        <v>46186</v>
+        <v>46180</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="3">
+        <v>60713035</v>
+      </c>
+      <c r="G32" s="3">
         <v>9</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3">
-        <v>60220066</v>
-      </c>
-      <c r="G32" s="3">
-        <v>11</v>
-      </c>
       <c r="H32" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" s="4"/>
+      <c r="M32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="K32" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -2249,17 +2255,17 @@
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2277,17 +2283,17 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -2301,21 +2307,21 @@
         <v>46188</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -2326,61 +2332,55 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
-        <v>46168</v>
+        <v>46189</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="6">
-        <v>0.76041666666666663</v>
+      <c r="C36" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F36" s="3">
-        <v>60713039</v>
+        <v>60220067</v>
       </c>
       <c r="G36" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="K36" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O36" s="3"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
       <c r="P36" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>43</v>
@@ -2389,19 +2389,19 @@
         <v>44</v>
       </c>
       <c r="F37" s="3">
-        <v>60220067</v>
+        <v>60220077</v>
       </c>
       <c r="G37" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="K37" s="3" t="b">
         <v>1</v>
@@ -2411,18 +2411,18 @@
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
-        <v>46196</v>
+        <v>46245</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>43</v>
@@ -2431,19 +2431,19 @@
         <v>44</v>
       </c>
       <c r="F38" s="3">
-        <v>60220077</v>
+        <v>60220080</v>
       </c>
       <c r="G38" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="K38" s="3" t="b">
         <v>1</v>
@@ -2454,107 +2454,181 @@
       <c r="O38" s="4"/>
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
+      <c r="A39" s="9">
+        <v>46252</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F39" s="11">
+        <v>60716043</v>
+      </c>
+      <c r="G39" s="11">
+        <v>11</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="K39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" s="13"/>
+      <c r="M39" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
     </row>
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="A40" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="3">
+        <v>60220087</v>
+      </c>
+      <c r="G40" s="3">
+        <v>15</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8"/>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
+      <c r="A41" s="9">
+        <v>46259</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="11">
+        <v>60220093</v>
+      </c>
+      <c r="G41" s="11">
+        <v>16</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="K41" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
-        <v>46245</v>
+        <v>46260</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F42" s="3">
-        <v>60220080</v>
+        <v>60713048</v>
       </c>
       <c r="G42" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="K42" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
+      <c r="M42" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>60</v>
@@ -2563,96 +2637,100 @@
         <v>61</v>
       </c>
       <c r="F43" s="3">
-        <v>60716043</v>
+        <v>60716048</v>
       </c>
       <c r="G43" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="K43" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
     </row>
     <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
-        <v>46257</v>
+        <v>46266</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F44" s="3">
-        <v>60220087</v>
+        <v>60716052</v>
       </c>
       <c r="G44" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K44" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F45" s="3">
-        <v>60220093</v>
+        <v>60713051</v>
       </c>
       <c r="G45" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>57</v>
@@ -2660,55 +2738,57 @@
       <c r="K45" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L45" s="4"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
+      <c r="L45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
     </row>
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
-        <v>46260</v>
+        <v>46271</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F46" s="3">
-        <v>60713048</v>
+        <v>60220097</v>
       </c>
       <c r="G46" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K46" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
-        <v>46261</v>
+        <v>46273</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>10</v>
@@ -2723,16 +2803,16 @@
         <v>61</v>
       </c>
       <c r="F47" s="3">
-        <v>60716048</v>
+        <v>60716055</v>
       </c>
       <c r="G47" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>57</v>
@@ -2740,86 +2820,88 @@
       <c r="K47" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L47" s="4"/>
+      <c r="L47" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="M47" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
+        <v>85</v>
+      </c>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
     </row>
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F48" s="3">
-        <v>60716052</v>
+        <v>60713054</v>
       </c>
       <c r="G48" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K48" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>52</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
-        <v>46267</v>
+        <v>46281</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F49" s="3">
-        <v>60713051</v>
+        <v>60220113</v>
       </c>
       <c r="G49" s="3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="K49" s="3" t="b">
         <v>1</v>
@@ -2827,60 +2909,66 @@
       <c r="L49" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="M49" s="3"/>
       <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
+      <c r="O49" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
-        <v>46271</v>
+        <v>46281</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F50" s="3">
-        <v>60220097</v>
+        <v>60713060</v>
       </c>
       <c r="G50" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K50" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
+      <c r="L50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>55</v>
+        <v>7</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.84375</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>60</v>
@@ -2889,176 +2977,162 @@
         <v>61</v>
       </c>
       <c r="F51" s="3">
-        <v>60716055</v>
+        <v>60716058</v>
       </c>
       <c r="G51" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="K51" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>52</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="N51" s="3"/>
-      <c r="O51" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="O51" s="3"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
-        <v>46275</v>
+        <v>46287</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F52" s="3">
-        <v>60713054</v>
+        <v>60220119</v>
       </c>
       <c r="G52" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="K52" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>0.84375</v>
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F53" s="3">
-        <v>60716058</v>
+        <v>60713064</v>
       </c>
       <c r="G53" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="K53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>52</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L53" s="4"/>
       <c r="M53" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
-        <v>46281</v>
+        <v>46290</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F54" s="3">
-        <v>60713060</v>
+        <v>60716062</v>
       </c>
       <c r="G54" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="K54" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="L54" s="4"/>
       <c r="M54" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
-        <v>46281</v>
+        <v>46295</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>42</v>
+      <c r="C55" s="8">
+        <v>0.84375</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>43</v>
@@ -3067,19 +3141,19 @@
         <v>44</v>
       </c>
       <c r="F55" s="3">
-        <v>60220113</v>
+        <v>60220066</v>
       </c>
       <c r="G55" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="K55" s="3" t="b">
         <v>1</v>
@@ -3089,58 +3163,62 @@
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F56" s="3">
-        <v>60220119</v>
+        <v>60716068</v>
       </c>
       <c r="G56" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="K56" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
+      <c r="L56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
@@ -3149,80 +3227,82 @@
         <v>49</v>
       </c>
       <c r="F57" s="3">
-        <v>60713064</v>
+        <v>60713066</v>
       </c>
       <c r="G57" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="K57" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L57" s="4"/>
+      <c r="L57" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="M57" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F58" s="3">
-        <v>60716062</v>
+        <v>60220122</v>
       </c>
       <c r="G58" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="K58" s="3" t="b">
         <v>1</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>60</v>
@@ -3231,43 +3311,39 @@
         <v>61</v>
       </c>
       <c r="F59" s="3">
-        <v>60716068</v>
+        <v>60716069</v>
       </c>
       <c r="G59" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="K59" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="L59" s="4"/>
       <c r="M59" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
-        <v>46297</v>
+        <v>46303</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -3276,43 +3352,39 @@
         <v>49</v>
       </c>
       <c r="F60" s="3">
-        <v>60713066</v>
+        <v>60713071</v>
       </c>
       <c r="G60" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="K60" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="L60" s="4"/>
       <c r="M60" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
     </row>
     <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>43</v>
@@ -3321,19 +3393,19 @@
         <v>44</v>
       </c>
       <c r="F61" s="3">
-        <v>60220122</v>
+        <v>60220132</v>
       </c>
       <c r="G61" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="K61" s="3" t="b">
         <v>1</v>
@@ -3344,125 +3416,51 @@
       <c r="O61" s="4"/>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="2">
-        <v>46301</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" s="3">
-        <v>60716069</v>
-      </c>
-      <c r="G62" s="3">
-        <v>18</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K62" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4"/>
-      <c r="M62" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
     </row>
     <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="2">
-        <v>46303</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F63" s="3">
-        <v>60713071</v>
-      </c>
-      <c r="G63" s="3">
-        <v>18</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K63" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L63" s="4"/>
-      <c r="M63" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3"/>
     </row>
     <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="2">
-        <v>46306</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" s="3">
-        <v>60220132</v>
-      </c>
-      <c r="G64" s="3">
-        <v>22</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
+      <c r="A64" s="10"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4405,7 +4403,11 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:O64" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:O64" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O64">
+      <sortCondition ref="A1:A64"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="A2:O33 P8:P9 P11:P12 P15:P16 P32:P35 A34:D35 F34:O35 A36:O64">
     <cfRule type="expression" dxfId="15" priority="1">
       <formula>$O2="ALLA TRE (DAM+VIT+SVART)"</formula>
